--- a/Material/SmartClock_Materialliste.xlsx
+++ b/Material/SmartClock_Materialliste.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bldsg-my.sharepoint.com/personal/sai_ragavan_edu_gbssg_ch/Documents/Dokumente/Schule/ims-t/IP/SmartClock/ims.project.smartclock/Material/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saira\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="397" documentId="8_{462786D1-4C4F-43AD-9779-E11ABC312B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0492E387-3810-47C3-B7D3-72EE3FC27B95}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105374E3-5829-427B-8771-048959F164DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4DF3711A-0043-4D27-B00E-AB9931E5E226}"/>
+    <workbookView xWindow="28680" yWindow="-1665" windowWidth="29040" windowHeight="15720" xr2:uid="{4DF3711A-0043-4D27-B00E-AB9931E5E226}"/>
   </bookViews>
   <sheets>
     <sheet name="Materialliste" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="77">
   <si>
     <t xml:space="preserve">Anzahl </t>
   </si>
@@ -246,6 +246,27 @@
   </si>
   <si>
     <t>Verbindung der Komponente</t>
+  </si>
+  <si>
+    <t>Thumb Slide Joystick</t>
+  </si>
+  <si>
+    <t>1568-09426-ND</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.digikey.de/de/products/detail/sparkfun-electronics/09426/7319630?s=N4IgTCBcDaIMIHkCyBaADATgCxgGwgF0BfIA</t>
+  </si>
+  <si>
+    <t>Qwiic Button</t>
+  </si>
+  <si>
+    <t>1568-15932-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.de/de/products/detail/sparkfun-electronics/15932/11570499?s=N4IgTCBcDaIEIHk4FoCMBWAnAZggXQF8g</t>
+  </si>
+  <si>
+    <t>Joystick zur Anwendung der Funktion</t>
   </si>
 </sst>
 </file>
@@ -302,7 +323,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -317,7 +338,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -344,8 +370,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC90F75E-5801-4028-ABDA-8A43427BCB16}" name="Tabelle2" displayName="Tabelle2" ref="C8:K20" totalsRowShown="0">
-  <autoFilter ref="C8:K20" xr:uid="{DC90F75E-5801-4028-ABDA-8A43427BCB16}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC90F75E-5801-4028-ABDA-8A43427BCB16}" name="Tabelle2" displayName="Tabelle2" ref="C8:K21" totalsRowShown="0">
+  <autoFilter ref="C8:K21" xr:uid="{DC90F75E-5801-4028-ABDA-8A43427BCB16}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -853,33 +879,32 @@
       </c>
     </row>
     <row r="12" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="8">
+      <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>27</v>
+        <v>71</v>
+      </c>
+      <c r="G12" s="9">
+        <v>9426</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="I12" s="6">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="J12" s="6">
-        <f>(I12*C12)</f>
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="K12" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="3:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1091,12 +1116,42 @@
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C20">
-        <f>SUM(C9:C19)</f>
-        <v>14</v>
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="9">
+        <v>15932</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="6">
+        <v>4.6500000000000004</v>
       </c>
       <c r="J20" s="6">
-        <f>SUM(J9:J19)</f>
-        <v>139.34999999999997</v>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="K20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <f>SUM(C9:C20)</f>
+        <v>15</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="J21" s="6">
+        <f>SUM(J9:J20)</f>
+        <v>142.9</v>
       </c>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.25">
@@ -1430,7 +1485,7 @@
     <hyperlink ref="H11" r:id="rId2" xr:uid="{DFB435C1-0A70-486F-998C-232C50E345CE}"/>
     <hyperlink ref="H15" r:id="rId3" xr:uid="{53F7DD62-9941-49C5-B05C-26E60EF7827E}"/>
     <hyperlink ref="H14" r:id="rId4" xr:uid="{C5C04C26-EF4B-49E4-84D8-151226AA66FD}"/>
-    <hyperlink ref="H12" r:id="rId5" xr:uid="{FA11A680-01ED-4D0D-B8E5-EBF6D706BD6E}"/>
+    <hyperlink ref="H12" r:id="rId5" display="https://www.sparkfun.com/sparkfun-qwiic-directional-pad.html" xr:uid="{FA11A680-01ED-4D0D-B8E5-EBF6D706BD6E}"/>
     <hyperlink ref="H16" r:id="rId6" xr:uid="{AFB8E1DB-0BD6-4AC1-B9E6-C45495ED2520}"/>
     <hyperlink ref="H13" r:id="rId7" xr:uid="{6830E33F-34A5-4356-B295-A18C5BBC8E1C}"/>
     <hyperlink ref="H9" r:id="rId8" xr:uid="{D45C9B21-0747-4DB4-8971-5B4BC2FE15D0}"/>
